--- a/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="11_652E137AF52521E58F19B0408CBE37AD98A83948" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9184AD8A-DEDD-4841-BC4B-F8C921F27B70}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="11_652E137AF52521E58F19B0408CBE37AD98A83948" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3817D64-B684-4386-A1C4-D69EAB3E13D5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="127">
   <si>
     <t>Project ID</t>
   </si>
@@ -147,6 +150,9 @@
   </si>
   <si>
     <t>GHG Emission Reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">million </t>
   </si>
   <si>
     <t>This is forest offsets related project</t>
@@ -184,9 +190,6 @@
   </si>
   <si>
     <t>VF</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
   </si>
   <si>
     <t>Consumer awareness of 
@@ -263,6 +266,121 @@
   </si>
   <si>
     <t xml:space="preserve">
+At least 7,500 customers 
+(including at least 4,000 women) 
+participate in rebate or coupon 
+programs, with an 80 percent 
+completion rate of required 
+surveys
+The project was under suspension, which was lifted in 2023</t>
+  </si>
+  <si>
+    <t>De-risking Renewable Energy Investment</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t>Number of 
+direct project beneficiaries</t>
+  </si>
+  <si>
+    <t>Mid-term target is met: over 5,000 people (60% women) are expected to benefit from solar plant in Shaulder region after a site-specific auction, supported by the Project. The figure is not yet confirmed. The number of beneficiaries of the 2 MWt project supported via the bonds issuance and the 0.5 MWt power plant that refused the subsidy is to be confirmed.</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>25 policy –makers 
+trained
+Capacity of 
+the Government to design and 
+implement policy initiatives enabling 
+development of renewable energy 
+market</t>
+  </si>
+  <si>
+    <t>he Government has 
+limited capacity to 
+deliver renewable 
+energy derisking 
+strategies</t>
+  </si>
+  <si>
+    <t>Mid-term target is met: knowledge gaps were identified; a capacity building plan was implemented:
+- 3 study tours to Netherlands, Finland and Denmark for policy makers were organized;
+- 7 regional workshops (2018) were organized to clarify the procedures of RE auctions in six regions of Kazakhstan. Over 70 potential investors and representatives of municipal authorities participated.
+- 7 renewable energy auctions workshops in three regions of Kazakhstan were organized for more than 200 potential investors, representatives of state bodies, 2 webinars were held in 2019;
+- participation and seminars at events - 2 RES summits in 2019, a seminar at Financial Settlement Center of Renewable Energy LLP and Power Expo Kazakhstan.</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>Government Capacity-Building</t>
+  </si>
+  <si>
+    <t>Renewable EnergyEnergy Infrastructure</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>Mid-term target is met: business and financial models are designed for key market sectors for testing in selected pilot projects. 
+9500 small-scale 
+projects</t>
+  </si>
+  <si>
+    <t>to the CO: Please estimate the number of MW.</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Financing Model</t>
+  </si>
+  <si>
+    <t>Urban NAMA</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Number of people
+benefiting from the
+improved transport
+and urban systems</t>
+  </si>
+  <si>
+    <t>The target is achieved - 238,936 people benefitted from the improved transport and urban systems (including 115,606 women and 23,181 children).</t>
+  </si>
+  <si>
+    <t>Just transition – green biofuel to benefit women in rural areas of 
+Kazakhstan.</t>
+  </si>
+  <si>
+    <t>Number of households covered 
+with trainings (60%women) on 
+gender equality and climate</t>
+  </si>
+  <si>
+    <t>500 HH</t>
+  </si>
+  <si>
+    <t>Pilot of production cycle 
+implemented</t>
+  </si>
+  <si>
+    <t>Access to clean heating (biofuel)</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 At least 7,5000 customers 
 (including at least 4,000 women) 
 participate in rebate or coupon 
@@ -270,105 +388,6 @@
 completion rate of required 
 surveys
 The project was under suspension, which was lifted in 2023</t>
-  </si>
-  <si>
-    <t>De-risking Renewable Energy Investment</t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
-    <t>Number of 
-direct project beneficiaries</t>
-  </si>
-  <si>
-    <t>Mid-term target is met: over 5,000 people (60% women) are expected to benefit from solar plant in Shaulder region after a site-specific auction, supported by the Project. The figure is not yet confirmed. The number of beneficiaries of the 2 MWt project supported via the bonds issuance and the 0.5 MWt power plant that refused the subsidy is to be confirmed.</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
-  </si>
-  <si>
-    <t>25 policy –makers 
-trained
-Capacity of 
-the Government to design and 
-implement policy initiatives enabling 
-development of renewable energy 
-market</t>
-  </si>
-  <si>
-    <t>he Government has 
-limited capacity to 
-deliver renewable 
-energy derisking 
-strategies</t>
-  </si>
-  <si>
-    <t>Mid-term target is met: knowledge gaps were identified; a capacity building plan was implemented:
-- 3 study tours to Netherlands, Finland and Denmark for policy makers were organized;
-- 7 regional workshops (2018) were organized to clarify the procedures of RE auctions in six regions of Kazakhstan. Over 70 potential investors and representatives of municipal authorities participated.
-- 7 renewable energy auctions workshops in three regions of Kazakhstan were organized for more than 200 potential investors, representatives of state bodies, 2 webinars were held in 2019;
-- participation and seminars at events - 2 RES summits in 2019, a seminar at Financial Settlement Center of Renewable Energy LLP and Power Expo Kazakhstan.</t>
-  </si>
-  <si>
-    <t>Renewable Energy</t>
-  </si>
-  <si>
-    <t>Government Capacity-Building</t>
-  </si>
-  <si>
-    <t>Renewable EnergyEnergy Infrastructure</t>
-  </si>
-  <si>
-    <t>`</t>
-  </si>
-  <si>
-    <t>Mid-term target is met: business and financial models are designed for key market sectors for testing in selected pilot projects. 
-9500 small-scale 
-projects</t>
-  </si>
-  <si>
-    <t>to the CO: Please estimate the number of MW.</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>Financing Model</t>
-  </si>
-  <si>
-    <t>Urban NAMA</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Number of people
-benefiting from the
-improved transport
-and urban systems</t>
-  </si>
-  <si>
-    <t>The target is achieved - 238,936 people benefitted from the improved transport and urban systems (including 115,606 women and 23,181 children).</t>
-  </si>
-  <si>
-    <t>Just transition – green biofuel to benefit women in rural areas of 
-Kazakhstan.</t>
-  </si>
-  <si>
-    <t>Number of households covered 
-with trainings (60%women) on 
-gender equality and climate</t>
-  </si>
-  <si>
-    <t>500 HH</t>
-  </si>
-  <si>
-    <t>Pilot of production cycle 
-implemented</t>
-  </si>
-  <si>
-    <t>Access to clean heating (biofuel)</t>
   </si>
   <si>
     <t>Education Services</t>
@@ -408,9 +427,6 @@
     <t>The project was under suspension, which was lifted in 2023</t>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
     <t>28,500 people, 50% 
 women</t>
   </si>
@@ -521,7 +537,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,8 +579,14 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF737373"/>
+      <name val="ProximaNova"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,8 +635,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -733,6 +761,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -741,7 +802,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -807,37 +868,10 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -848,6 +882,159 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -857,9 +1044,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1166,635 +1366,640 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D652C6A9-5991-4EDB-A8A4-AE884E7D9343}">
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="7" max="7" width="35.42578125" customWidth="1"/>
     <col min="8" max="8" width="21.140625" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" customWidth="1"/>
+    <col min="9" max="9" width="50.85546875" customWidth="1"/>
     <col min="13" max="13" width="67.5703125" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:19" ht="45.75">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="15"/>
-    </row>
-    <row r="2" spans="1:20" ht="83.25" customHeight="1">
-      <c r="A2" s="11">
+    </row>
+    <row r="2" spans="1:19" ht="105" customHeight="1">
+      <c r="A2" s="41">
         <v>136365</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="41">
         <v>304251</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="20">
         <v>0</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="20">
         <v>1400</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="42" t="s">
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15" t="s">
+      <c r="M2" s="44"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-    </row>
-    <row r="3" spans="1:20" ht="95.25" customHeight="1">
-      <c r="A3" s="15">
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+    </row>
+    <row r="3" spans="1:19" ht="167.25" customHeight="1">
+      <c r="A3" s="20">
         <v>130007</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="20">
         <v>2425796</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14">
+      <c r="G3" s="20"/>
+      <c r="H3" s="20">
         <v>450</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="19">
+      <c r="J3" s="20"/>
+      <c r="K3" s="46">
         <v>0.33</v>
       </c>
-      <c r="L3" s="43" t="s">
+      <c r="L3" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="21"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15" t="s">
+      <c r="M3" s="44"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-    </row>
-    <row r="4" spans="1:20" ht="63" customHeight="1">
-      <c r="A4" s="15">
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+    </row>
+    <row r="4" spans="1:19" ht="63" customHeight="1">
+      <c r="A4" s="55">
         <v>112788</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="55">
         <v>1214842</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13" t="s">
+      <c r="F4" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="43" t="s">
+      <c r="G4" s="75"/>
+      <c r="H4" s="94">
+        <v>5000000</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-    </row>
-    <row r="5" spans="1:20" ht="103.5" customHeight="1">
-      <c r="A5" s="32">
+      <c r="M4" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+    </row>
+    <row r="5" spans="1:19" ht="103.5" customHeight="1">
+      <c r="A5" s="58">
         <v>5703</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="32">
+      <c r="C5" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="56">
         <v>3500000</v>
       </c>
-      <c r="E5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="G5" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="H5" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="44" t="s">
+      <c r="I5" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="22"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-    </row>
-    <row r="6" spans="1:20" ht="188.45" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="16" t="s">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="M5" s="48"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+    </row>
+    <row r="6" spans="1:19" ht="188.45" customHeight="1">
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="25" t="s">
+      <c r="H6" s="77"/>
+      <c r="I6" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="40" t="s">
+      <c r="J6" s="54"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-    </row>
-    <row r="7" spans="1:20" ht="144.94999999999999" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="16" t="s">
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+    </row>
+    <row r="7" spans="1:19" ht="144.94999999999999" customHeight="1">
+      <c r="A7" s="62"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="47">
         <v>20</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15" t="s">
+      <c r="J7" s="54"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15" t="s">
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="15" t="s">
+      <c r="S7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="T7" s="15"/>
-    </row>
-    <row r="8" spans="1:20" ht="159.6" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="14" t="s">
+    </row>
+    <row r="8" spans="1:19" ht="159.6" customHeight="1">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="19">
+      <c r="J8" s="20"/>
+      <c r="K8" s="46">
         <f>4000/7500</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="L8" s="46"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15" t="s">
+      <c r="L8" s="59"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-    </row>
-    <row r="9" spans="1:20" ht="167.25">
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+    </row>
+    <row r="9" spans="1:19" ht="167.25">
       <c r="A9" s="29">
         <v>5490</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="35" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="29">
+        <v>39</v>
+      </c>
+      <c r="D9" s="63">
         <v>4510000</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="71">
         <v>0</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="72">
         <v>28500</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="19">
+      <c r="J9" s="20"/>
+      <c r="K9" s="46">
         <v>0.6</v>
       </c>
-      <c r="L9" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9" s="22"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15" t="s">
+      <c r="L9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="48"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="15" t="s">
+      <c r="P9" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-    </row>
-    <row r="10" spans="1:20" ht="234.75" customHeight="1">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="16" t="s">
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="29"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+    </row>
+    <row r="11" spans="1:19" ht="234.75" customHeight="1">
+      <c r="A11" s="29"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="17">
+      <c r="G11" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="71">
         <v>25</v>
       </c>
-      <c r="I10" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15" t="s">
+      <c r="I11" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15" t="s">
+      <c r="P11" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="S10" s="15" t="s">
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="T10" s="15"/>
-    </row>
-    <row r="11" spans="1:20" ht="91.5">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="16" t="s">
+      <c r="S11" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="91.5">
+      <c r="A12" s="30"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="14">
+      <c r="F12" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="20">
         <v>0</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H12" s="20">
         <v>9500</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="21" t="s">
+      <c r="I12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15" t="s">
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="P11" s="15" t="s">
+      <c r="N12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="S11" s="15" t="s">
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="S12" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="T11" s="15"/>
-    </row>
-    <row r="12" spans="1:20" ht="76.5">
-      <c r="A12" s="15">
+    </row>
+    <row r="13" spans="1:19" ht="76.5">
+      <c r="A13" s="55">
         <v>4670</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="B13" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="55">
         <v>5930000</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="14" t="s">
+      <c r="E13" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="27">
+      <c r="F13" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="73">
         <v>238936</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12" s="22"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15" t="s">
+      <c r="I13" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="48"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-    </row>
-    <row r="13" spans="1:20" ht="87" customHeight="1">
-      <c r="A13" s="32">
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+    </row>
+    <row r="14" spans="1:19" ht="87" customHeight="1">
+      <c r="A14" s="58">
         <v>125105</v>
       </c>
-      <c r="B13" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32">
+      <c r="B14" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="56">
         <v>300000</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E14" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15" t="s">
+      <c r="F14" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="19">
+      <c r="G14" s="20"/>
+      <c r="H14" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="46">
         <v>0.6</v>
       </c>
-      <c r="L13" s="44" t="s">
+      <c r="L14" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="22"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15">
+      <c r="M14" s="48"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+    </row>
+    <row r="15" spans="1:19" ht="43.5" customHeight="1">
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="21" t="s">
+      <c r="I15" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="L9:L11"/>
+  <mergeCells count="1">
+    <mergeCell ref="L14:L15"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S14" xr:uid="{FF02EA9A-25F1-44FE-9762-C6E48B264AA6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S15" xr:uid="{FF02EA9A-25F1-44FE-9762-C6E48B264AA6}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R14" xr:uid="{6F084E5F-2A8F-4FD2-81E1-4B73CFE7842A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R15" xr:uid="{6F084E5F-2A8F-4FD2-81E1-4B73CFE7842A}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q14" xr:uid="{8667D527-8F04-4B44-85D0-3846B36BEC0F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q15" xr:uid="{8667D527-8F04-4B44-85D0-3846B36BEC0F}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P14" xr:uid="{B93A8927-73BA-404E-A448-7FFB04CA5135}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P15" xr:uid="{B93A8927-73BA-404E-A448-7FFB04CA5135}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O14" xr:uid="{96CB3550-7BA7-4635-93A3-DBACF6BD966F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O15" xr:uid="{96CB3550-7BA7-4635-93A3-DBACF6BD966F}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{63FCFC0C-AA18-4E2D-9AFF-E8304122EAB6}"/>
@@ -1813,7 +2018,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E3 E5:E11 E13:E24</xm:sqref>
+          <xm:sqref>E2:E3 E5:E12 E14:E25</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1869,7 +2074,7 @@
       <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="9" t="s">
@@ -1925,7 +2130,7 @@
       </c>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
-      <c r="L2" s="42" t="s">
+      <c r="L2" s="33" t="s">
         <v>24</v>
       </c>
       <c r="M2" s="21"/>
@@ -1971,7 +2176,7 @@
       <c r="K3" s="19">
         <v>0.33</v>
       </c>
-      <c r="L3" s="43" t="s">
+      <c r="L3" s="34" t="s">
         <v>24</v>
       </c>
       <c r="M3" s="21"/>
@@ -2007,15 +2212,15 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="34" t="s">
         <v>24</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
@@ -2026,37 +2231,37 @@
       <c r="T4" s="15"/>
     </row>
     <row r="5" spans="1:20" ht="103.5" customHeight="1">
-      <c r="A5" s="32">
+      <c r="A5" s="82">
         <v>5703</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="32">
+      <c r="C5" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="82">
         <v>3500000</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="44" t="s">
-        <v>44</v>
+      <c r="L5" s="86" t="s">
+        <v>45</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="15"/>
@@ -2068,12 +2273,12 @@
       <c r="T5" s="15"/>
     </row>
     <row r="6" spans="1:20" ht="188.45" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
       <c r="E6" s="16" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>46</v>
@@ -2087,8 +2292,8 @@
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="40" t="s">
+      <c r="L6" s="87"/>
+      <c r="M6" s="31" t="s">
         <v>49</v>
       </c>
       <c r="N6" s="15"/>
@@ -2100,10 +2305,10 @@
       <c r="T6" s="15"/>
     </row>
     <row r="7" spans="1:20" ht="144.94999999999999" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
       <c r="E7" s="16" t="s">
         <v>50</v>
       </c>
@@ -2121,7 +2326,7 @@
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="45"/>
+      <c r="L7" s="87"/>
       <c r="M7" s="21"/>
       <c r="N7" s="15"/>
       <c r="O7" s="15" t="s">
@@ -2140,12 +2345,12 @@
       <c r="T7" s="15"/>
     </row>
     <row r="8" spans="1:20" ht="159.6" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
       <c r="E8" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>55</v>
@@ -2157,14 +2362,14 @@
         <v>57</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="19">
         <f>4000/7500</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="L8" s="46"/>
+      <c r="L8" s="88"/>
       <c r="M8" s="22"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15" t="s">
@@ -2179,16 +2384,16 @@
       <c r="T8" s="15"/>
     </row>
     <row r="9" spans="1:20" ht="167.25">
-      <c r="A9" s="29">
+      <c r="A9" s="83">
         <v>5490</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="C9" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="83">
         <v>4510000</v>
       </c>
       <c r="E9" s="16" t="s">
@@ -2210,8 +2415,8 @@
       <c r="K9" s="19">
         <v>0.6</v>
       </c>
-      <c r="L9" s="44" t="s">
-        <v>44</v>
+      <c r="L9" s="86" t="s">
+        <v>45</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="15"/>
@@ -2227,55 +2432,55 @@
       <c r="T9" s="15"/>
     </row>
     <row r="10" spans="1:20" ht="234.75" customHeight="1">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
+      <c r="A10" s="84"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
       <c r="E10" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H10" s="17">
         <v>25</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="45"/>
+      <c r="L10" s="87"/>
       <c r="M10" s="22"/>
       <c r="N10" s="15"/>
       <c r="O10" s="15" t="s">
         <v>25</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q10" s="15"/>
       <c r="R10" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="S10" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T10" s="15"/>
     </row>
     <row r="11" spans="1:20" ht="91.5">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
       <c r="E11" s="16" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="14">
         <v>0</v>
@@ -2284,24 +2489,24 @@
         <v>9500</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="46"/>
+      <c r="L11" s="88"/>
       <c r="M11" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P11" s="15" t="s">
         <v>60</v>
       </c>
       <c r="Q11" s="15"/>
       <c r="R11" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S11" s="15" t="s">
         <v>60</v>
@@ -2313,31 +2518,31 @@
         <v>4670</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="15">
         <v>5930000</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="27">
         <v>238936</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="47" t="s">
-        <v>44</v>
+      <c r="L12" s="37" t="s">
+        <v>45</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="15"/>
@@ -2353,32 +2558,32 @@
       <c r="T12" s="15"/>
     </row>
     <row r="13" spans="1:20" ht="87" customHeight="1">
-      <c r="A13" s="32">
+      <c r="A13" s="82">
         <v>125105</v>
       </c>
-      <c r="B13" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32">
+      <c r="B13" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82">
         <v>300000</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="15"/>
       <c r="K13" s="19">
         <v>0.6</v>
       </c>
-      <c r="L13" s="44" t="s">
+      <c r="L13" s="86" t="s">
         <v>24</v>
       </c>
       <c r="M13" s="22"/>
@@ -2391,24 +2596,24 @@
       <c r="T13" s="15"/>
     </row>
     <row r="14" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="15"/>
       <c r="F14" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15">
         <v>1</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="46"/>
+      <c r="L14" s="88"/>
       <c r="M14" s="21" t="s">
         <v>49</v>
       </c>
@@ -2422,6 +2627,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L13:L14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="C5:C8"/>
@@ -2432,11 +2642,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{60EFCDB0-223F-4A4D-B6F5-BBDC24BF85A5}"/>
@@ -2537,7 +2742,7 @@
         <v>304251</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>22</v>
@@ -2573,10 +2778,10 @@
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2597,40 +2802,40 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="101.45">
       <c r="A5">
         <v>5703</v>
       </c>
-      <c r="B5" s="48" t="s">
-        <v>37</v>
+      <c r="B5" s="95" t="s">
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>3500000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="188.45">
-      <c r="B6" s="48"/>
+      <c r="B6" s="95"/>
       <c r="E6" s="3" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>46</v>
@@ -2639,14 +2844,14 @@
         <v>47</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="144.94999999999999">
-      <c r="B7" s="48"/>
+      <c r="B7" s="95"/>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>51</v>
@@ -2660,7 +2865,7 @@
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="159.6">
-      <c r="B8" s="48"/>
+      <c r="B8" s="95"/>
       <c r="E8" s="3"/>
       <c r="F8" s="7" t="s">
         <v>55</v>
@@ -2669,10 +2874,10 @@
         <v>56</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="159.6">
@@ -2683,13 +2888,13 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9">
         <v>4510000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>61</v>
@@ -2698,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>62</v>
@@ -2709,33 +2914,33 @@
         <v>21</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.95">
       <c r="E11" s="3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="7">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72.599999999999994">
@@ -2743,32 +2948,32 @@
         <v>4670</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12">
         <v>5930000</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>180000</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="87">
       <c r="A13">
         <v>125105</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>79</v>
+      <c r="B13" s="89" t="s">
+        <v>80</v>
       </c>
       <c r="D13">
         <v>300000</v>
@@ -2777,7 +2982,7 @@
         <v>21</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13">
         <v>500</v>
@@ -2785,18 +2990,18 @@
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="43.5">
-      <c r="B14" s="48"/>
+      <c r="B14" s="95"/>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2836,160 +3041,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="36" t="s">
-        <v>100</v>
+      <c r="A2" s="90" t="s">
+        <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="36"/>
+      <c r="A3" s="90"/>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="36"/>
+      <c r="A4" s="90"/>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="37" t="s">
-        <v>104</v>
+      <c r="A5" s="91" t="s">
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="91"/>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="91"/>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="91"/>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="37"/>
+      <c r="A9" s="91"/>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="38" t="s">
-        <v>113</v>
+      <c r="A10" s="92" t="s">
+        <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="38"/>
+      <c r="A11" s="92"/>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="39" t="s">
-        <v>116</v>
+      <c r="A12" s="93" t="s">
+        <v>118</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="39"/>
+      <c r="A13" s="93"/>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="39"/>
+      <c r="A14" s="93"/>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3004,26 +3209,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3272,8 +3457,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E152319-825F-40FF-A1D2-C8F0D68E3D5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78E0917F-458B-4639-A6C5-A70FE0FCDA82}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3281,5 +3486,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78E0917F-458B-4639-A6C5-A70FE0FCDA82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E152319-825F-40FF-A1D2-C8F0D68E3D5D}"/>
 </file>
--- a/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="11_652E137AF52521E58F19B0408CBE37AD98A83948" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CAD6BEA-17E6-4159-9A83-E490AC16EACF}"/>
+  <xr:revisionPtr revIDLastSave="415" documentId="11_652E137AF52521E58F19B0408CBE37AD98A83948" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C70ECBE-1D55-477D-8603-0E123A47D414}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,7 +193,7 @@
     <t>PIMS+</t>
   </si>
   <si>
-    <t>Other Energy Services</t>
+    <t>Energy Efficiency Services</t>
   </si>
   <si>
     <t>Number of households 
@@ -427,6 +427,9 @@
     <t>GHG Emission Reduction</t>
   </si>
   <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 At least 7,5000 customers 
 (including at least 4,000 women) 
@@ -539,9 +542,6 @@
   </si>
   <si>
     <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
-  </si>
-  <si>
-    <t>Energy Efficiency Services</t>
   </si>
   <si>
     <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
@@ -847,7 +847,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1061,6 +1061,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1070,47 +1106,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1691,9 +1688,9 @@
       <c r="AG4" s="18"/>
     </row>
     <row r="5" spans="1:33" ht="106.5">
-      <c r="A5" s="94"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="85"/>
       <c r="D5" s="52"/>
       <c r="E5" s="51" t="s">
         <v>19</v>
@@ -1703,7 +1700,7 @@
       </c>
       <c r="G5" s="70"/>
       <c r="H5" s="72"/>
-      <c r="I5" s="96"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="35"/>
@@ -1726,7 +1723,7 @@
         <v>44</v>
       </c>
       <c r="U5" s="80"/>
-      <c r="Y5" s="94"/>
+      <c r="Y5" s="84"/>
       <c r="Z5" s="41"/>
       <c r="AA5" s="18"/>
       <c r="AB5" s="18"/>
@@ -1737,13 +1734,13 @@
       <c r="AG5" s="18"/>
     </row>
     <row r="6" spans="1:33" ht="103.5" customHeight="1">
-      <c r="A6" s="91">
+      <c r="A6" s="81">
         <v>5703</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="81" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="67">
@@ -1797,7 +1794,7 @@
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
       <c r="D7" s="57"/>
-      <c r="E7" s="92"/>
+      <c r="E7" s="82"/>
       <c r="F7" s="70" t="s">
         <v>53</v>
       </c>
@@ -2217,13 +2214,13 @@
       <c r="AG14" s="18"/>
     </row>
     <row r="15" spans="1:33" ht="87" customHeight="1">
-      <c r="A15" s="91">
+      <c r="A15" s="81">
         <v>125105</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="86" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="67">
@@ -2275,7 +2272,7 @@
       <c r="B16" s="55"/>
       <c r="C16" s="55"/>
       <c r="D16" s="53"/>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="83" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="70" t="s">
@@ -2601,16 +2598,16 @@
       <c r="T4" s="13"/>
     </row>
     <row r="5" spans="1:20" ht="103.5" customHeight="1">
-      <c r="A5" s="84">
+      <c r="A5" s="89">
         <v>5703</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="84">
+      <c r="D5" s="89">
         <v>3500000</v>
       </c>
       <c r="E5" s="14" t="s">
@@ -2630,7 +2627,7 @@
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="81" t="s">
+      <c r="L5" s="93" t="s">
         <v>52</v>
       </c>
       <c r="M5" s="20"/>
@@ -2643,12 +2640,12 @@
       <c r="T5" s="13"/>
     </row>
     <row r="6" spans="1:20" ht="188.45" customHeight="1">
-      <c r="A6" s="84"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
       <c r="E6" s="14" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>53</v>
@@ -2662,7 +2659,7 @@
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="82"/>
+      <c r="L6" s="94"/>
       <c r="M6" s="29" t="s">
         <v>56</v>
       </c>
@@ -2675,10 +2672,10 @@
       <c r="T6" s="13"/>
     </row>
     <row r="7" spans="1:20" ht="144.94999999999999" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
+      <c r="A7" s="89"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
       <c r="E7" s="14" t="s">
         <v>57</v>
       </c>
@@ -2696,7 +2693,7 @@
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="82"/>
+      <c r="L7" s="94"/>
       <c r="M7" s="19"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="s">
@@ -2715,10 +2712,10 @@
       <c r="T7" s="13"/>
     </row>
     <row r="8" spans="1:20" ht="159.6" customHeight="1">
-      <c r="A8" s="84"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
+      <c r="A8" s="89"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
       <c r="E8" s="11" t="s">
         <v>62</v>
       </c>
@@ -2732,14 +2729,14 @@
         <v>65</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="17">
         <f>4000/7500</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="L8" s="83"/>
+      <c r="L8" s="95"/>
       <c r="M8" s="20"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
@@ -2754,16 +2751,16 @@
       <c r="T8" s="13"/>
     </row>
     <row r="9" spans="1:20" ht="167.25">
-      <c r="A9" s="87">
+      <c r="A9" s="90">
         <v>5490</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="87">
+      <c r="D9" s="90">
         <v>4510000</v>
       </c>
       <c r="E9" s="14" t="s">
@@ -2785,7 +2782,7 @@
       <c r="K9" s="17">
         <v>0.6</v>
       </c>
-      <c r="L9" s="81" t="s">
+      <c r="L9" s="93" t="s">
         <v>52</v>
       </c>
       <c r="M9" s="20"/>
@@ -2802,10 +2799,10 @@
       <c r="T9" s="13"/>
     </row>
     <row r="10" spans="1:20" ht="234.75" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
+      <c r="A10" s="91"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="14" t="s">
         <v>19</v>
       </c>
@@ -2823,7 +2820,7 @@
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="82"/>
+      <c r="L10" s="94"/>
       <c r="M10" s="20"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
@@ -2842,10 +2839,10 @@
       <c r="T10" s="13"/>
     </row>
     <row r="11" spans="1:20" ht="91.5">
-      <c r="A11" s="89"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
       <c r="E11" s="14" t="s">
         <v>31</v>
       </c>
@@ -2863,7 +2860,7 @@
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
-      <c r="L11" s="83"/>
+      <c r="L11" s="95"/>
       <c r="M11" s="19" t="s">
         <v>80</v>
       </c>
@@ -2897,7 +2894,7 @@
         <v>5930000</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>85</v>
@@ -2928,14 +2925,14 @@
       <c r="T12" s="13"/>
     </row>
     <row r="13" spans="1:20" ht="87" customHeight="1">
-      <c r="A13" s="84">
+      <c r="A13" s="89">
         <v>125105</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84">
+      <c r="C13" s="89"/>
+      <c r="D13" s="89">
         <v>300000</v>
       </c>
       <c r="E13" s="13" t="s">
@@ -2953,7 +2950,7 @@
       <c r="K13" s="17">
         <v>0.6</v>
       </c>
-      <c r="L13" s="81" t="s">
+      <c r="L13" s="93" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="20"/>
@@ -2966,10 +2963,10 @@
       <c r="T13" s="13"/>
     </row>
     <row r="14" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
+      <c r="A14" s="89"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="13"/>
       <c r="F14" s="18" t="s">
         <v>92</v>
@@ -2983,7 +2980,7 @@
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="83"/>
+      <c r="L14" s="95"/>
       <c r="M14" s="19" t="s">
         <v>56</v>
       </c>
@@ -2997,6 +2994,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L13:L14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="C5:C8"/>
@@ -3007,11 +3009,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{60EFCDB0-223F-4A4D-B6F5-BBDC24BF85A5}"/>
@@ -3112,7 +3109,7 @@
         <v>304251</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>24</v>
@@ -3148,10 +3145,10 @@
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3179,7 +3176,7 @@
       <c r="A5">
         <v>5703</v>
       </c>
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="97" t="s">
         <v>45</v>
       </c>
       <c r="C5" t="s">
@@ -3198,14 +3195,14 @@
         <v>49</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="188.45">
-      <c r="B6" s="98"/>
+      <c r="B6" s="97"/>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>53</v>
@@ -3214,12 +3211,12 @@
         <v>54</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="144.94999999999999">
-      <c r="B7" s="98"/>
+      <c r="B7" s="97"/>
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
@@ -3235,7 +3232,7 @@
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="159.6">
-      <c r="B8" s="98"/>
+      <c r="B8" s="97"/>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
         <v>63</v>
@@ -3244,10 +3241,10 @@
         <v>64</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="159.6">
@@ -3273,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>70</v>
@@ -3284,13 +3281,13 @@
         <v>98</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>75</v>
@@ -3307,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72.599999999999994">
@@ -3342,7 +3339,7 @@
       <c r="A13">
         <v>125105</v>
       </c>
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="96" t="s">
         <v>88</v>
       </c>
       <c r="D13">
@@ -3360,9 +3357,9 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="43.5">
-      <c r="B14" s="98"/>
+      <c r="B14" s="97"/>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>92</v>
@@ -3418,87 +3415,87 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="98" t="s">
         <v>68</v>
       </c>
       <c r="B2" s="74" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="98" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="99" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="74" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="99" t="s">
-        <v>114</v>
-      </c>
       <c r="B4" s="74" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="99" t="s">
-        <v>118</v>
+      <c r="A5" s="98" t="s">
+        <v>119</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="99" t="s">
-        <v>120</v>
+      <c r="A6" s="98" t="s">
+        <v>121</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="99" t="s">
-        <v>122</v>
+      <c r="A7" s="98" t="s">
+        <v>123</v>
       </c>
       <c r="B7" s="74" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="99" t="s">
-        <v>124</v>
+      <c r="A8" s="98" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="99" t="s">
-        <v>102</v>
+      <c r="A9" s="98" t="s">
+        <v>103</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="100" t="s">
-        <v>127</v>
+      <c r="B10" s="99" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="99" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="98" t="s">
         <v>130</v>
       </c>
       <c r="B12" s="74" t="s">
@@ -3506,39 +3503,39 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="100" t="s">
+      <c r="A13" s="98" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="99" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="99" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="99" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="100" t="s">
+      <c r="B16" s="99" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="98" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="74" t="s">
@@ -3546,42 +3543,42 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="98" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="100" t="s">
+      <c r="B18" s="99" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="100" t="s">
+      <c r="B19" s="99" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="100" t="s">
+      <c r="B20" s="99" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="101" t="s">
+      <c r="B21" s="100" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="99" t="s">
+      <c r="A22" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="100" t="s">
+      <c r="B22" s="99" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3591,17 +3588,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3626,6 +3625,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3705,6 +3705,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3849,24 +3854,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFC866BA-E0E2-463C-B854-038ECE867413}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E152319-825F-40FF-A1D2-C8F0D68E3D5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78E0917F-458B-4639-A6C5-A70FE0FCDA82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B7EEB1-3A6F-4E80-9CEE-7E002D3EE09B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E152319-825F-40FF-A1D2-C8F0D68E3D5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFC866BA-E0E2-463C-B854-038ECE867413}"/>
 </file>
--- a/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28627"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415" documentId="11_652E137AF52521E58F19B0408CBE37AD98A83948" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C70ECBE-1D55-477D-8603-0E123A47D414}"/>
+  <xr:revisionPtr revIDLastSave="458" documentId="11_652E137AF52521E58F19B0408CBE37AD98A83948" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D425B97-3A70-43A1-95BD-058087126D0F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="160">
   <si>
     <t>Project ID</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Policy Population</t>
+  </si>
+  <si>
+    <t>project document</t>
   </si>
   <si>
     <t>EE and Retrofits in Turkestan Secondary School</t>
@@ -128,6 +131,9 @@
   </si>
   <si>
     <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Aleksandra: changed budget as per the info from the CO.</t>
   </si>
   <si>
     <t>Attracting investors in the field of energy efficiency</t>
@@ -162,6 +168,9 @@
   </si>
   <si>
     <t>This is forest offsets related project</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
   <si>
     <t>to the CO: Please estimate the amount of GHG reduction.</t>
@@ -172,7 +181,7 @@
 implementation of forest
 carbon projects are
 developed and submitted
-to state bodies_x000D_</t>
+to state bodies</t>
   </si>
   <si>
     <t>Renewable Energy</t>
@@ -190,7 +199,7 @@
     <t>UNEP Efficient Appliances Global PFD</t>
   </si>
   <si>
-    <t>PIMS+</t>
+    <t>https://co.pims.undp.org/project/view?id=5703</t>
   </si>
   <si>
     <t>Energy Efficiency Services</t>
@@ -213,6 +222,9 @@
   </si>
   <si>
     <t>1.3 million households purchase</t>
+  </si>
+  <si>
+    <t>GEF</t>
   </si>
   <si>
     <t>VF</t>
@@ -307,6 +319,9 @@
     <t>De-risking Renewable Energy Investment</t>
   </si>
   <si>
+    <t>https://co.pims.undp.org/project/view?id=5490</t>
+  </si>
+  <si>
     <t>Electricity Access</t>
   </si>
   <si>
@@ -318,6 +333,14 @@
   </si>
   <si>
     <t>Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment from CO: We propose combining the four outputs into one:
+Small-scale projects of total installed capacity of 9.5 MW addressing various technologies and sectors are implemented with support from the project was achieved.
+1) GHG Emission reduction – 1,041,174 tCO2eq direct lifetime emissions reduction verified;
+2) Total number of beneficiaries – over 4.75 million for 24 commissioned and verified projects and the first RE project under the site-specific auction mechanism. This number of beneficiaries was estimated and verified by the Project’s technical experts. Information on beneficiaries was included in their reports. This included the 50 MW site-specific auction green bond financed scheme, and the 2 MW solar power plant both in Shaulder village, Turkestan region that are operational and feeding into the regional grid. The number of beneficiaries for these projects is derived from data provided by the National Bureau of Statistics, which reflects the population of the corresponding territories.
+Installed capacity added – 14.1 MW
+</t>
   </si>
   <si>
     <t>Energy (MW added)</t>
@@ -369,7 +392,11 @@
     <t>Financing Model</t>
   </si>
   <si>
-    <t>Urban NAMA</t>
+    <t>Urban NAMA
+Overall, NAMA investments on energy efficiency have contributed to an improved quality of life, creating a healthier and more sustainable environment for 311,799 beneficiaries (of which 58% are women and children). The Project has provided strong support to the GoK to develop and implement NAMAs in the urban sector to achieve voluntary national GHG emission reduction targets. This has resulted in a strong commitment by the GoK to continue with EE technology demonstrations, especially related to building modernization that includes heating and hot water systems modernization and the insulation of the building envelope.</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=4670</t>
   </si>
   <si>
     <t>Transportation and E-mobility Services</t>
@@ -381,10 +408,19 @@
 and urban systems</t>
   </si>
   <si>
+    <t>311,799</t>
+  </si>
+  <si>
     <t>The target is achieved - 238,936 people benefitted from the improved transport and urban systems (including 115,606 women and 23,181 children).</t>
   </si>
   <si>
+    <t>148 928 (50%)</t>
+  </si>
+  <si>
     <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleksandra: GHG Emission reduction – 1, 105 063 tCO2eq direct lifetime emissions reduction verified; changed the number of beneficiaries; added description. </t>
   </si>
   <si>
     <t>Just transition – green biofuel to benefit women in rural areas of 
@@ -402,6 +438,12 @@
     <t>500 HH</t>
   </si>
   <si>
+    <t>Trained 507 households (including 80% women) in Kazakhstan on gender equality and climate as part of a project promoting a just transition to green biofuel in rural areas.</t>
+  </si>
+  <si>
+    <t>Aleksandra: changed number of beneficiaries, % of women.</t>
+  </si>
+  <si>
     <t>Pilot of production cycle 
 implemented</t>
   </si>
@@ -425,6 +467,9 @@
   </si>
   <si>
     <t>GHG Emission Reduction</t>
+  </si>
+  <si>
+    <t>PIMS+</t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -440,6 +485,9 @@
 The project was under suspension, which was lifted in 2023</t>
   </si>
   <si>
+    <t>Urban NAMA</t>
+  </si>
+  <si>
     <t>Transport Services</t>
   </si>
   <si>
@@ -599,7 +647,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,6 +712,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -842,17 +898,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -868,7 +921,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -882,7 +935,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -939,7 +992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -948,7 +1001,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -990,7 +1043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1004,9 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1073,11 +1123,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1085,9 +1162,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1095,15 +1169,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1424,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D652C6A9-5991-4EDB-A8A4-AE884E7D9343}">
-  <dimension ref="A1:AG16"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
@@ -1444,9 +1509,10 @@
     <col min="19" max="19" width="12.28515625" customWidth="1"/>
     <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="44.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="45.75">
+    <row r="1" spans="1:34" ht="45.75">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
@@ -1480,55 +1546,58 @@
       <c r="K1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="76" t="s">
+      <c r="M1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="75" t="s">
+      <c r="N1" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="75" t="s">
+      <c r="O1" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="76" t="s">
+      <c r="P1" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="76" t="s">
+      <c r="Q1" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="77" t="s">
+      <c r="R1" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="78" t="s">
+      <c r="S1" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="77" t="s">
+      <c r="T1" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="78" t="s">
+      <c r="U1" s="77" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" ht="105" customHeight="1">
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="105" customHeight="1">
       <c r="A2" s="38">
         <v>136365</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="38">
-        <v>304251</v>
+        <v>150000</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="18">
         <v>0</v>
@@ -1537,147 +1606,156 @@
         <v>1400</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
       <c r="L2" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="79" t="s">
-        <v>27</v>
+      <c r="N2" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
-      <c r="S2" s="80"/>
+      <c r="S2" s="79"/>
       <c r="T2" s="9"/>
-      <c r="U2" s="80"/>
+      <c r="U2" s="79"/>
       <c r="Y2" s="40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z2" s="41"/>
       <c r="AA2" s="18"/>
       <c r="AB2" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC2" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD2" s="9"/>
       <c r="AE2" s="18"/>
       <c r="AF2" s="18"/>
       <c r="AG2" s="18"/>
-    </row>
-    <row r="3" spans="1:33" ht="167.25" customHeight="1">
+      <c r="AH2" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" ht="167.25" customHeight="1">
       <c r="A3" s="18">
         <v>130007</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="18">
-        <v>2425796</v>
+        <v>32</v>
+      </c>
+      <c r="D3" s="89">
+        <v>8325000</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="18">
         <v>450</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J3" s="18"/>
       <c r="K3" s="43">
         <v>0.33</v>
       </c>
       <c r="L3" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="9"/>
-      <c r="N3" s="79" t="s">
-        <v>27</v>
+      <c r="N3" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
-      <c r="S3" s="80"/>
+      <c r="S3" s="79"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="80"/>
+      <c r="U3" s="79"/>
       <c r="Y3" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z3" s="41"/>
       <c r="AA3" s="18"/>
       <c r="AB3" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC3" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD3" s="9"/>
       <c r="AE3" s="18"/>
       <c r="AF3" s="18"/>
       <c r="AG3" s="18"/>
-    </row>
-    <row r="4" spans="1:33" ht="63" customHeight="1">
+      <c r="AH3" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="63" customHeight="1">
       <c r="A4" s="52">
         <v>112788</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="52">
-        <v>1214842</v>
+        <v>37</v>
+      </c>
+      <c r="D4" s="90">
+        <v>798748</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="72">
+        <v>38</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="69"/>
+      <c r="H4" s="71">
         <v>5000000</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="9"/>
-      <c r="N4" s="79" t="s">
-        <v>27</v>
+      <c r="N4" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="79"/>
       <c r="T4" s="9"/>
-      <c r="U4" s="80"/>
+      <c r="U4" s="79"/>
+      <c r="V4" t="s">
+        <v>41</v>
+      </c>
       <c r="Y4" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z4" s="41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AA4" s="18"/>
       <c r="AB4" s="18"/>
@@ -1686,44 +1764,47 @@
       <c r="AE4" s="18"/>
       <c r="AF4" s="18"/>
       <c r="AG4" s="18"/>
-    </row>
-    <row r="5" spans="1:33" ht="106.5">
-      <c r="A5" s="84"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="85"/>
+      <c r="AH4" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="91.5">
+      <c r="A5" s="83"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
       <c r="D5" s="52"/>
       <c r="E5" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="70"/>
-      <c r="H5" s="72"/>
+      <c r="F5" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="69"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="4"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="35"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="79" t="s">
-        <v>27</v>
+      <c r="N5" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="S5" s="80"/>
+        <v>46</v>
+      </c>
+      <c r="S5" s="79"/>
       <c r="T5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="U5" s="80"/>
-      <c r="Y5" s="84"/>
+        <v>47</v>
+      </c>
+      <c r="U5" s="79"/>
+      <c r="Y5" s="83"/>
       <c r="Z5" s="41"/>
       <c r="AA5" s="18"/>
       <c r="AB5" s="18"/>
@@ -1733,52 +1814,54 @@
       <c r="AF5" s="18"/>
       <c r="AG5" s="18"/>
     </row>
-    <row r="6" spans="1:33" ht="103.5" customHeight="1">
-      <c r="A6" s="81">
+    <row r="6" spans="1:34" ht="103.5" customHeight="1">
+      <c r="A6" s="80">
         <v>5703</v>
       </c>
-      <c r="B6" s="81" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="81" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="67">
+      <c r="B6" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="66">
         <v>3500000</v>
       </c>
-      <c r="E6" s="62" t="s">
-        <v>47</v>
+      <c r="E6" s="61" t="s">
+        <v>50</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="63" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="18"/>
+        <v>53</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K6" s="18"/>
       <c r="L6" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M6" s="9"/>
-      <c r="N6" s="79" t="s">
-        <v>27</v>
+      <c r="N6" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
-      <c r="S6" s="80"/>
+      <c r="S6" s="79"/>
       <c r="T6" s="9"/>
-      <c r="U6" s="80"/>
+      <c r="U6" s="79"/>
       <c r="Y6" s="54" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Z6" s="45"/>
       <c r="AA6" s="18"/>
@@ -1789,41 +1872,43 @@
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
     </row>
-    <row r="7" spans="1:33" ht="188.45" customHeight="1">
+    <row r="7" spans="1:34" ht="188.45" customHeight="1">
       <c r="A7" s="58"/>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
       <c r="D7" s="57"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="71"/>
-      <c r="I7" s="64" t="s">
+      <c r="E7" s="81"/>
+      <c r="F7" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="70"/>
+      <c r="I7" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="51"/>
       <c r="K7" s="18"/>
       <c r="L7" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M7" s="9"/>
-      <c r="N7" s="79" t="s">
-        <v>27</v>
+      <c r="N7" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
-      <c r="S7" s="80"/>
+      <c r="S7" s="79"/>
       <c r="T7" s="9"/>
-      <c r="U7" s="80"/>
+      <c r="U7" s="79"/>
       <c r="Y7" s="58"/>
       <c r="Z7" s="46" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AA7" s="18"/>
       <c r="AB7" s="18"/>
@@ -1833,208 +1918,219 @@
       <c r="AF7" s="18"/>
       <c r="AG7" s="18"/>
     </row>
-    <row r="8" spans="1:33" ht="144.94999999999999" customHeight="1">
+    <row r="8" spans="1:34" ht="144.94999999999999" customHeight="1">
       <c r="A8" s="58"/>
       <c r="B8" s="58"/>
       <c r="C8" s="58"/>
       <c r="D8" s="57"/>
-      <c r="E8" s="62" t="s">
-        <v>57</v>
+      <c r="E8" s="61" t="s">
+        <v>61</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H8" s="44">
         <v>20</v>
       </c>
-      <c r="I8" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" s="51"/>
+      <c r="I8" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K8" s="18"/>
       <c r="L8" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M8" s="9"/>
-      <c r="N8" s="79" t="s">
-        <v>27</v>
+      <c r="N8" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
-      <c r="S8" s="80"/>
+      <c r="S8" s="79"/>
       <c r="T8" s="9"/>
-      <c r="U8" s="80"/>
+      <c r="U8" s="79"/>
       <c r="Y8" s="58"/>
       <c r="Z8" s="41"/>
       <c r="AA8" s="18"/>
       <c r="AB8" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC8" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD8" s="9"/>
       <c r="AE8" s="18"/>
       <c r="AF8" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AG8" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" ht="159.6" customHeight="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" ht="159.6" customHeight="1">
       <c r="A9" s="55"/>
       <c r="B9" s="55"/>
       <c r="C9" s="55"/>
       <c r="D9" s="53"/>
       <c r="E9" s="51" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="18"/>
+        <v>68</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K9" s="43">
         <f>4000/7500</f>
         <v>0.53333333333333333</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M9" s="9"/>
-      <c r="N9" s="79" t="s">
-        <v>27</v>
+      <c r="N9" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
-      <c r="S9" s="80"/>
+      <c r="S9" s="79"/>
       <c r="T9" s="9"/>
-      <c r="U9" s="80"/>
+      <c r="U9" s="79"/>
       <c r="Y9" s="55"/>
       <c r="Z9" s="45"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC9" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD9" s="9"/>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
       <c r="AG9" s="18"/>
     </row>
-    <row r="10" spans="1:33" ht="106.5">
+    <row r="10" spans="1:34" ht="381.75">
       <c r="A10" s="28">
         <v>5490</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>46</v>
+        <v>71</v>
+      </c>
+      <c r="C10" s="87" t="s">
+        <v>72</v>
       </c>
       <c r="D10" s="60">
         <v>4510000</v>
       </c>
-      <c r="E10" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="67">
+      <c r="E10" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="66">
         <v>0</v>
       </c>
-      <c r="H10" s="68">
+      <c r="H10" s="67">
         <v>28500</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="18"/>
+        <v>75</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K10" s="43">
         <v>0.6</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M10" s="9"/>
-      <c r="N10" s="79" t="s">
-        <v>27</v>
+      <c r="N10" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
-      <c r="S10" s="80" t="s">
-        <v>71</v>
+      <c r="S10" s="79" t="s">
+        <v>76</v>
       </c>
       <c r="T10" s="9"/>
-      <c r="U10" s="80"/>
+      <c r="U10" s="79"/>
       <c r="Y10" s="48" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Z10" s="45"/>
       <c r="AA10" s="18"/>
       <c r="AB10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC10" s="18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AD10" s="9"/>
       <c r="AE10" s="18"/>
       <c r="AF10" s="18"/>
       <c r="AG10" s="18"/>
-    </row>
-    <row r="11" spans="1:33" ht="45.75">
+      <c r="AH10" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" ht="45.75">
       <c r="A11" s="27"/>
       <c r="B11" s="33"/>
       <c r="C11" s="27"/>
       <c r="D11" s="59"/>
-      <c r="E11" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
+      <c r="E11" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
       <c r="H11" s="18">
         <v>2.5</v>
       </c>
-      <c r="J11" s="18"/>
+      <c r="J11" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K11" s="43"/>
       <c r="L11" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M11" s="9"/>
-      <c r="N11" s="79" t="s">
-        <v>27</v>
+      <c r="N11" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="80" t="s">
-        <v>71</v>
+      <c r="S11" s="79" t="s">
+        <v>76</v>
       </c>
       <c r="T11" s="9"/>
-      <c r="U11" s="80"/>
+      <c r="U11" s="79"/>
       <c r="Y11" s="49"/>
       <c r="Z11" s="45"/>
       <c r="AA11" s="18"/>
@@ -2045,70 +2141,72 @@
       <c r="AF11" s="18"/>
       <c r="AG11" s="18"/>
     </row>
-    <row r="12" spans="1:33" ht="234.75" customHeight="1">
+    <row r="12" spans="1:34" ht="234.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="33"/>
       <c r="C12" s="27"/>
       <c r="D12" s="59"/>
-      <c r="E12" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="67" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="67">
+      <c r="E12" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="66">
         <v>25</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12" s="18"/>
+        <v>81</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K12" s="18"/>
       <c r="L12" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M12" s="9"/>
-      <c r="N12" s="79" t="s">
-        <v>27</v>
+      <c r="N12" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="80"/>
+      <c r="S12" s="79"/>
       <c r="T12" s="9"/>
-      <c r="U12" s="80"/>
+      <c r="U12" s="79"/>
       <c r="Y12" s="49"/>
       <c r="Z12" s="45"/>
       <c r="AA12" s="18"/>
       <c r="AB12" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC12" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AD12" s="9"/>
       <c r="AE12" s="18"/>
       <c r="AF12" s="18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AG12" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" ht="83.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="83.25">
       <c r="A13" s="28"/>
       <c r="B13" s="34"/>
       <c r="C13" s="28"/>
       <c r="D13" s="60"/>
-      <c r="E13" s="67" t="s">
-        <v>31</v>
+      <c r="E13" s="66" t="s">
+        <v>33</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G13" s="18">
         <v>0</v>
@@ -2117,146 +2215,160 @@
         <v>9500</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="18"/>
+        <v>85</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="K13" s="18"/>
       <c r="L13" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M13" s="9"/>
-      <c r="N13" s="79" t="s">
-        <v>27</v>
+      <c r="N13" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="80"/>
+      <c r="S13" s="79"/>
       <c r="T13" s="9"/>
-      <c r="U13" s="80"/>
+      <c r="U13" s="79"/>
       <c r="Y13" s="50"/>
       <c r="Z13" s="41" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AA13" s="18"/>
       <c r="AB13" s="18" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AC13" s="18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AD13" s="9"/>
       <c r="AE13" s="18"/>
       <c r="AF13" s="18" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="AG13" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" ht="60.75">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="321">
       <c r="A14" s="52">
         <v>4670</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>46</v>
+        <v>89</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>90</v>
       </c>
       <c r="D14" s="52">
         <v>5930000</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G14" s="18"/>
-      <c r="H14" s="69">
-        <v>238936</v>
+      <c r="H14" s="68" t="s">
+        <v>93</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
+        <v>94</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>95</v>
+      </c>
       <c r="L14" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M14" s="9"/>
-      <c r="N14" s="79" t="s">
-        <v>87</v>
+      <c r="N14" s="78" t="s">
+        <v>96</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="80"/>
+      <c r="S14" s="79"/>
       <c r="T14" s="9"/>
-      <c r="U14" s="80"/>
+      <c r="U14" s="79"/>
       <c r="Y14" s="47" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Z14" s="45"/>
       <c r="AA14" s="18"/>
       <c r="AB14" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC14" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD14" s="9"/>
       <c r="AE14" s="18"/>
       <c r="AF14" s="18"/>
       <c r="AG14" s="18"/>
-    </row>
-    <row r="15" spans="1:33" ht="87" customHeight="1">
-      <c r="A15" s="81">
+      <c r="AH14" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="87" customHeight="1">
+      <c r="A15" s="80">
         <v>125105</v>
       </c>
-      <c r="B15" s="81" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="86" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="67">
+      <c r="B15" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="66">
         <v>300000</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="18"/>
+        <v>101</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>102</v>
+      </c>
       <c r="J15" s="18"/>
       <c r="K15" s="43">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M15" s="9"/>
-      <c r="N15" s="79" t="s">
-        <v>27</v>
+      <c r="N15" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="80"/>
+      <c r="S15" s="79"/>
       <c r="T15" s="9"/>
-      <c r="U15" s="80"/>
+      <c r="U15" s="79"/>
+      <c r="V15" t="s">
+        <v>41</v>
+      </c>
       <c r="Y15" s="54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z15" s="45"/>
       <c r="AA15" s="18"/>
@@ -2266,60 +2378,63 @@
       <c r="AE15" s="18"/>
       <c r="AF15" s="18"/>
       <c r="AG15" s="18"/>
-    </row>
-    <row r="16" spans="1:33" ht="43.5" customHeight="1">
+      <c r="AH15" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="43.5" customHeight="1">
       <c r="A16" s="55"/>
       <c r="B16" s="55"/>
       <c r="C16" s="55"/>
       <c r="D16" s="53"/>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70">
+      <c r="F16" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69">
         <v>1</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="9"/>
-      <c r="N16" s="79" t="s">
-        <v>27</v>
+      <c r="N16" s="78" t="s">
+        <v>28</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="9" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="S16" s="80"/>
+        <v>44</v>
+      </c>
+      <c r="S16" s="79"/>
       <c r="T16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="U16" s="80"/>
+        <v>47</v>
+      </c>
+      <c r="U16" s="79"/>
       <c r="Y16" s="55"/>
       <c r="Z16" s="41" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AA16" s="18"/>
       <c r="AB16" s="18"/>
       <c r="AC16" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AD16" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="AE16" s="18"/>
       <c r="AF16" s="18"/>
@@ -2369,6 +2484,9 @@
     <hyperlink ref="C3" r:id="rId2" xr:uid="{D60912F9-4304-48E6-937B-DD0DCE8123BF}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{0D3BE250-2550-40B1-BB5A-85C1930B13EF}"/>
     <hyperlink ref="C15" r:id="rId4" xr:uid="{44CCD078-7CE5-4137-9602-09E780DCEE3A}"/>
+    <hyperlink ref="C14" r:id="rId5" xr:uid="{E495D9B7-9F9D-4A64-97AF-43B9FC40750B}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{11760844-2F4F-4043-AFC7-D6BF6D8E8EAC}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{557E8BF8-1D45-4F46-8949-2688F03659E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2442,10 +2560,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>12</v>
@@ -2472,19 +2590,19 @@
         <v>136365</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="9">
         <v>304251</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="11">
         <v>0</v>
@@ -2493,20 +2611,20 @@
         <v>1400</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="19"/>
       <c r="N2" s="13"/>
       <c r="O2" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
@@ -2518,41 +2636,41 @@
         <v>130007</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" s="13">
         <v>2425796</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="12">
         <v>450</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="17">
         <v>0.33</v>
       </c>
       <c r="L3" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="19"/>
       <c r="N3" s="13"/>
       <c r="O3" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
@@ -2564,30 +2682,30 @@
         <v>112788</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="13">
         <v>1214842</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="L4" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -2598,37 +2716,37 @@
       <c r="T4" s="13"/>
     </row>
     <row r="5" spans="1:20" ht="103.5" customHeight="1">
-      <c r="A5" s="89">
+      <c r="A5" s="94">
         <v>5703</v>
       </c>
-      <c r="B5" s="89" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="89">
+      <c r="B5" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="94">
         <v>3500000</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="93" t="s">
-        <v>52</v>
+      <c r="L5" s="91" t="s">
+        <v>56</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="13"/>
@@ -2640,28 +2758,28 @@
       <c r="T5" s="13"/>
     </row>
     <row r="6" spans="1:20" ht="188.45" customHeight="1">
-      <c r="A6" s="89"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="14" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="94"/>
+      <c r="L6" s="92"/>
       <c r="M6" s="29" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
@@ -2672,78 +2790,78 @@
       <c r="T6" s="13"/>
     </row>
     <row r="7" spans="1:20" ht="144.94999999999999" customHeight="1">
-      <c r="A7" s="89"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
       <c r="E7" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H7" s="12">
         <v>20</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="94"/>
+      <c r="L7" s="92"/>
       <c r="M7" s="19"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="S7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T7" s="13"/>
     </row>
     <row r="8" spans="1:20" ht="159.6" customHeight="1">
-      <c r="A8" s="89"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
+      <c r="A8" s="94"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="17">
         <f>4000/7500</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="L8" s="95"/>
+      <c r="L8" s="93"/>
       <c r="M8" s="20"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
@@ -2751,23 +2869,23 @@
       <c r="T8" s="13"/>
     </row>
     <row r="9" spans="1:20" ht="167.25">
-      <c r="A9" s="90">
+      <c r="A9" s="97">
         <v>5490</v>
       </c>
-      <c r="B9" s="90" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="90" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="90">
+      <c r="B9" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="97">
         <v>4510000</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G9" s="15">
         <v>0</v>
@@ -2776,22 +2894,22 @@
         <v>28500</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="17">
         <v>0.6</v>
       </c>
-      <c r="L9" s="93" t="s">
-        <v>52</v>
+      <c r="L9" s="91" t="s">
+        <v>56</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
@@ -2799,55 +2917,55 @@
       <c r="T9" s="13"/>
     </row>
     <row r="10" spans="1:20" ht="234.75" customHeight="1">
-      <c r="A10" s="91"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
       <c r="E10" s="14" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H10" s="15">
         <v>25</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="94"/>
+      <c r="L10" s="92"/>
       <c r="M10" s="20"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="13"/>
       <c r="R10" s="13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="S10" s="13" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="T10" s="13"/>
     </row>
     <row r="11" spans="1:20" ht="91.5">
-      <c r="A11" s="92"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
@@ -2856,27 +2974,27 @@
         <v>9500</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
-      <c r="L11" s="95"/>
+      <c r="L11" s="93"/>
       <c r="M11" s="19" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q11" s="13"/>
       <c r="R11" s="13" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T11" s="13"/>
     </row>
@@ -2885,39 +3003,39 @@
         <v>4670</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D12" s="13">
         <v>5930000</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="25">
         <v>238936</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
@@ -2925,33 +3043,33 @@
       <c r="T12" s="13"/>
     </row>
     <row r="13" spans="1:20" ht="87" customHeight="1">
-      <c r="A13" s="89">
+      <c r="A13" s="94">
         <v>125105</v>
       </c>
-      <c r="B13" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89">
+      <c r="B13" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94">
         <v>300000</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="13"/>
       <c r="K13" s="17">
         <v>0.6</v>
       </c>
-      <c r="L13" s="93" t="s">
-        <v>26</v>
+      <c r="L13" s="91" t="s">
+        <v>27</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="13"/>
@@ -2963,26 +3081,26 @@
       <c r="T13" s="13"/>
     </row>
     <row r="14" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A14" s="89"/>
-      <c r="B14" s="88"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="13"/>
       <c r="F14" s="18" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13">
         <v>1</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="95"/>
+      <c r="L14" s="93"/>
       <c r="M14" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
@@ -2994,11 +3112,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="C5:C8"/>
@@ -3009,6 +3122,11 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="B5:B8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L13:L14"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{60EFCDB0-223F-4A4D-B6F5-BBDC24BF85A5}"/>
@@ -3100,19 +3218,19 @@
         <v>136365</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>304251</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -3121,7 +3239,7 @@
         <v>503</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="203.1">
@@ -3129,26 +3247,26 @@
         <v>130007</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>2425796</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="5" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3156,10 +3274,10 @@
         <v>112788</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>1214842</v>
@@ -3169,82 +3287,82 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="101.45">
       <c r="A5">
         <v>5703</v>
       </c>
-      <c r="B5" s="97" t="s">
-        <v>45</v>
+      <c r="B5" s="101" t="s">
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>3500000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="188.45">
-      <c r="B6" s="97"/>
+      <c r="B6" s="101"/>
       <c r="E6" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="144.94999999999999">
-      <c r="B7" s="97"/>
+      <c r="B7" s="101"/>
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="159.6">
-      <c r="B8" s="97"/>
+      <c r="B8" s="101"/>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="159.6">
@@ -3252,62 +3370,62 @@
         <v>5490</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D9">
         <v>4510000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="333.6">
       <c r="E10" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.95">
       <c r="E11" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72.599999999999994">
@@ -3315,41 +3433,41 @@
         <v>4670</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D12">
         <v>5930000</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>180000</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="87">
       <c r="A13">
         <v>125105</v>
       </c>
-      <c r="B13" s="96" t="s">
-        <v>88</v>
+      <c r="B13" s="100" t="s">
+        <v>98</v>
       </c>
       <c r="D13">
         <v>300000</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>500</v>
@@ -3357,18 +3475,18 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="43.5">
-      <c r="B14" s="97"/>
+      <c r="B14" s="101"/>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3407,179 +3525,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="72" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="98" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="74" t="s">
-        <v>116</v>
+      <c r="A2" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="74" t="s">
+      <c r="A3" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="102" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="102" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="102" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="73" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="102" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="102" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="73" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="102" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="98" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="74" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="98" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="74" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="98" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="74" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="98" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>127</v>
+      <c r="B9" s="73" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="99" t="s">
-        <v>128</v>
+      <c r="A10" s="102" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="103" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="99" t="s">
-        <v>129</v>
+      <c r="A11" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="98" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="74" t="s">
-        <v>131</v>
+      <c r="A12" s="102" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="99" t="s">
-        <v>132</v>
+      <c r="A13" s="102" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="103" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="98" t="s">
-        <v>133</v>
-      </c>
-      <c r="B14" s="99" t="s">
-        <v>134</v>
+      <c r="A14" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="103" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="99" t="s">
-        <v>135</v>
+      <c r="A15" s="102" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="103" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="98" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="99" t="s">
-        <v>136</v>
+      <c r="A16" s="102" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="103" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="98" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>137</v>
+      <c r="A17" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="73" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="98" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18" s="99" t="s">
-        <v>139</v>
+      <c r="A18" s="102" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="103" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="98" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="99" t="s">
-        <v>141</v>
+      <c r="A19" s="102" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" s="103" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="98" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="99" t="s">
-        <v>142</v>
+      <c r="A20" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="103" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="98" t="s">
+      <c r="A21" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="100" t="s">
-        <v>143</v>
+      <c r="B21" s="104" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="98" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="99" t="s">
-        <v>145</v>
+      <c r="A22" s="102" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="103" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -3588,17 +3706,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3853,6 +3960,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3863,11 +3981,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E152319-825F-40FF-A1D2-C8F0D68E3D5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B7EEB1-3A6F-4E80-9CEE-7E002D3EE09B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B7EEB1-3A6F-4E80-9CEE-7E002D3EE09B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E152319-825F-40FF-A1D2-C8F0D68E3D5D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kazakhstan - Energy Projects.xlsx
@@ -280,7 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -581,9 +581,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -679,6 +676,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K17" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1324,15 +1361,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="107" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="107" t="n"/>
-      <c r="M4" s="107" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M4" s="18" t="n"/>
       <c r="N4" s="18" t="n"/>
       <c r="O4" s="43" t="n"/>
       <c r="P4" s="94" t="n"/>
@@ -1819,9 +1852,8 @@
           <t>GEF</t>
         </is>
       </c>
-      <c r="O10" s="43">
-        <f>4000/7500</f>
-        <v/>
+      <c r="O10" s="43" t="n">
+        <v>0.5333333333333333</v>
       </c>
       <c r="P10" s="94" t="n"/>
       <c r="Q10" s="78" t="inlineStr">
@@ -1873,15 +1905,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="K11" s="107" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="110" t="n"/>
-      <c r="M11" s="111" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M11" s="65" t="n"/>
       <c r="N11" s="18" t="n"/>
       <c r="O11" s="43" t="n"/>
       <c r="P11" s="94" t="n"/>
@@ -1920,9 +1948,9 @@
       <c r="D12" s="60" t="n">
         <v>4510000</v>
       </c>
-      <c r="E12" s="112" t="n"/>
-      <c r="F12" s="112" t="n"/>
-      <c r="G12" s="112" t="n"/>
+      <c r="E12" s="111" t="n"/>
+      <c r="F12" s="111" t="n"/>
+      <c r="G12" s="111" t="n"/>
       <c r="H12" s="60" t="inlineStr">
         <is>
           <t>VF</t>
@@ -2249,9 +2277,9 @@
       <c r="D16" s="52" t="n">
         <v>5930000</v>
       </c>
-      <c r="E16" s="113" t="n"/>
-      <c r="F16" s="113" t="n"/>
-      <c r="G16" s="113" t="n"/>
+      <c r="E16" s="112" t="n"/>
+      <c r="F16" s="112" t="n"/>
+      <c r="G16" s="112" t="n"/>
       <c r="H16" s="52" t="inlineStr">
         <is>
           <t>VF</t>
@@ -2350,15 +2378,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="K17" s="107" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="114" t="n"/>
-      <c r="M17" s="107" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L17" s="113" t="n"/>
+      <c r="M17" s="18" t="n"/>
       <c r="N17" s="18" t="n"/>
       <c r="O17" s="18" t="n"/>
       <c r="P17" s="94" t="n"/>
@@ -2554,7 +2578,7 @@
       <c r="AJ19" s="18" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="15">
+  <dataValidations count="13">
     <dataValidation sqref="AG2:AG16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -2594,12 +2618,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -2607,6 +2625,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2972,10 +2991,10 @@
       <c r="T5" s="13" t="n"/>
     </row>
     <row r="6" ht="188.45" customHeight="1" s="101">
-      <c r="A6" s="115" t="n"/>
-      <c r="B6" s="115" t="n"/>
-      <c r="C6" s="115" t="n"/>
-      <c r="D6" s="115" t="n"/>
+      <c r="A6" s="114" t="n"/>
+      <c r="B6" s="114" t="n"/>
+      <c r="C6" s="114" t="n"/>
+      <c r="D6" s="114" t="n"/>
       <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
@@ -3020,7 +3039,7 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="13" t="n"/>
-      <c r="L6" s="116" t="n"/>
+      <c r="L6" s="115" t="n"/>
       <c r="M6" s="29" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.</t>
@@ -3035,10 +3054,10 @@
       <c r="T6" s="13" t="n"/>
     </row>
     <row r="7" ht="144.95" customHeight="1" s="101">
-      <c r="A7" s="115" t="n"/>
-      <c r="B7" s="115" t="n"/>
-      <c r="C7" s="115" t="n"/>
-      <c r="D7" s="115" t="n"/>
+      <c r="A7" s="114" t="n"/>
+      <c r="B7" s="114" t="n"/>
+      <c r="C7" s="114" t="n"/>
+      <c r="D7" s="114" t="n"/>
       <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -3076,7 +3095,7 @@
       </c>
       <c r="J7" s="13" t="n"/>
       <c r="K7" s="13" t="n"/>
-      <c r="L7" s="116" t="n"/>
+      <c r="L7" s="115" t="n"/>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="13" t="n"/>
       <c r="O7" s="13" t="inlineStr">
@@ -3103,10 +3122,10 @@
       <c r="T7" s="13" t="n"/>
     </row>
     <row r="8" ht="159.6" customHeight="1" s="101">
-      <c r="A8" s="117" t="n"/>
-      <c r="B8" s="117" t="n"/>
-      <c r="C8" s="117" t="n"/>
-      <c r="D8" s="117" t="n"/>
+      <c r="A8" s="116" t="n"/>
+      <c r="B8" s="116" t="n"/>
+      <c r="C8" s="116" t="n"/>
+      <c r="D8" s="116" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -3144,11 +3163,10 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="17">
-        <f>4000/7500</f>
-        <v/>
-      </c>
-      <c r="L8" s="118" t="n"/>
+      <c r="K8" s="17" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="L8" s="117" t="n"/>
       <c r="M8" s="20" t="n"/>
       <c r="N8" s="13" t="n"/>
       <c r="O8" s="13" t="inlineStr">
@@ -3232,10 +3250,10 @@
       <c r="T9" s="13" t="n"/>
     </row>
     <row r="10" ht="234.75" customHeight="1" s="101">
-      <c r="A10" s="115" t="n"/>
-      <c r="B10" s="115" t="n"/>
-      <c r="C10" s="115" t="n"/>
-      <c r="D10" s="115" t="n"/>
+      <c r="A10" s="114" t="n"/>
+      <c r="B10" s="114" t="n"/>
+      <c r="C10" s="114" t="n"/>
+      <c r="D10" s="114" t="n"/>
       <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -3275,7 +3293,7 @@
       </c>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
-      <c r="L10" s="116" t="n"/>
+      <c r="L10" s="115" t="n"/>
       <c r="M10" s="20" t="n"/>
       <c r="N10" s="13" t="n"/>
       <c r="O10" s="13" t="inlineStr">
@@ -3302,10 +3320,10 @@
       <c r="T10" s="13" t="n"/>
     </row>
     <row r="11" ht="91.5" customHeight="1" s="101">
-      <c r="A11" s="117" t="n"/>
-      <c r="B11" s="117" t="n"/>
-      <c r="C11" s="117" t="n"/>
-      <c r="D11" s="117" t="n"/>
+      <c r="A11" s="116" t="n"/>
+      <c r="B11" s="116" t="n"/>
+      <c r="C11" s="116" t="n"/>
+      <c r="D11" s="116" t="n"/>
       <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
@@ -3331,7 +3349,7 @@
       </c>
       <c r="J11" s="13" t="n"/>
       <c r="K11" s="13" t="n"/>
-      <c r="L11" s="118" t="n"/>
+      <c r="L11" s="117" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
           <t>to the CO: Please estimate the number of MW.</t>
@@ -3476,10 +3494,10 @@
       <c r="T13" s="13" t="n"/>
     </row>
     <row r="14" ht="43.5" customHeight="1" s="101">
-      <c r="A14" s="117" t="n"/>
-      <c r="B14" s="117" t="n"/>
-      <c r="C14" s="117" t="n"/>
-      <c r="D14" s="117" t="n"/>
+      <c r="A14" s="116" t="n"/>
+      <c r="B14" s="116" t="n"/>
+      <c r="C14" s="116" t="n"/>
+      <c r="D14" s="116" t="n"/>
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="18" t="inlineStr">
         <is>
@@ -3498,7 +3516,7 @@
       </c>
       <c r="J14" s="13" t="n"/>
       <c r="K14" s="13" t="n"/>
-      <c r="L14" s="118" t="n"/>
+      <c r="L14" s="117" t="n"/>
       <c r="M14" s="19" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.</t>
@@ -4121,288 +4139,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="119" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="119" t="inlineStr">
+      <c r="B1" s="118" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1" s="101">
-      <c r="A2" s="120" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="120" t="inlineStr">
+      <c r="B2" s="119" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="120" t="inlineStr">
+      <c r="A3" s="119" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="120" t="inlineStr">
+      <c r="B3" s="119" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" s="101">
-      <c r="A4" s="120" t="inlineStr">
+      <c r="A4" s="119" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="120" t="inlineStr">
+      <c r="B4" s="119" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1" s="101">
-      <c r="A5" s="120" t="inlineStr">
+      <c r="A5" s="119" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="120" t="inlineStr">
+      <c r="B5" s="119" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1" s="101">
-      <c r="A6" s="120" t="inlineStr">
+      <c r="A6" s="119" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="120" t="inlineStr">
+      <c r="B6" s="119" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1" s="101">
-      <c r="A7" s="120" t="inlineStr">
+      <c r="A7" s="119" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="120" t="inlineStr">
+      <c r="B7" s="119" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1" s="101">
-      <c r="A8" s="120" t="inlineStr">
+      <c r="A8" s="119" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="120" t="inlineStr">
+      <c r="B8" s="119" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="101">
-      <c r="A9" s="120" t="inlineStr">
+      <c r="A9" s="119" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="120" t="inlineStr">
+      <c r="B9" s="119" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1" s="101">
-      <c r="A10" s="120" t="inlineStr">
+      <c r="A10" s="119" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="120" t="inlineStr">
+      <c r="B10" s="119" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1" s="101">
-      <c r="A11" s="120" t="inlineStr">
+      <c r="A11" s="119" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="120" t="inlineStr">
+      <c r="B11" s="119" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1" s="101">
-      <c r="A12" s="120" t="inlineStr">
+      <c r="A12" s="119" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="120" t="inlineStr">
+      <c r="B12" s="119" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1" s="101">
-      <c r="A13" s="120" t="inlineStr">
+      <c r="A13" s="119" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="120" t="inlineStr">
+      <c r="B13" s="119" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="120" t="inlineStr">
+      <c r="A14" s="119" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="120" t="inlineStr">
+      <c r="B14" s="119" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1" s="101">
-      <c r="A15" s="120" t="inlineStr">
+      <c r="A15" s="119" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="120" t="inlineStr">
+      <c r="B15" s="119" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1" s="101">
-      <c r="A16" s="120" t="inlineStr">
+      <c r="A16" s="119" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="120" t="inlineStr">
+      <c r="B16" s="119" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1" s="101">
-      <c r="A17" s="120" t="inlineStr">
+      <c r="A17" s="119" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="120" t="inlineStr">
+      <c r="B17" s="119" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1" s="101">
-      <c r="A18" s="120" t="inlineStr">
+      <c r="A18" s="119" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="120" t="inlineStr">
+      <c r="B18" s="119" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1" s="101">
-      <c r="A19" s="120" t="inlineStr">
+      <c r="A19" s="119" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="120" t="inlineStr">
+      <c r="B19" s="119" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1" s="101">
-      <c r="A20" s="120" t="inlineStr">
+      <c r="A20" s="119" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="120" t="inlineStr">
+      <c r="B20" s="119" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1" s="101">
-      <c r="A21" s="120" t="inlineStr">
+      <c r="A21" s="119" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="120" t="inlineStr">
+      <c r="B21" s="119" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1" s="101">
-      <c r="A22" s="120" t="inlineStr">
+      <c r="A22" s="119" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="120" t="inlineStr">
+      <c r="B22" s="119" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="120" t="inlineStr">
+      <c r="A23" s="119" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="120" t="inlineStr">
+      <c r="B23" s="119" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="120" t="inlineStr">
+      <c r="A24" s="119" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="120" t="inlineStr">
+      <c r="B24" s="119" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
